--- a/data/trans_orig/Q17B-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q17B-Clase-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según número de veces que ha consultado al médico en las 2 últimas semanas</t>
+          <t>Número medio de veces que la población ha tenido una consulta médica en las 2 últimas semanas (tasa de respuesta: 99,19%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,7 +731,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,41</t>
+          <t>0,26; 0,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,42</t>
+          <t>0,25; 0,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -751,12 +751,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,41</t>
+          <t>0,29; 0,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,29</t>
+          <t>0,2; 0,28</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,38</t>
+          <t>0,27; 0,37</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,45</t>
+          <t>0,17; 0,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,45</t>
+          <t>0,3; 0,45</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,37</t>
+          <t>0,25; 0,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,38</t>
+          <t>0,28; 0,38</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,38</t>
+          <t>0,27; 0,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,29</t>
+          <t>0,06; 0,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,69</t>
+          <t>0,34; 0,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1026,17 +1026,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,49</t>
+          <t>0,32; 0,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,43</t>
+          <t>0,27; 0,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,36</t>
+          <t>0,26; 0,36</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,32</t>
+          <t>0,08; 0,31</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 0,48</t>
+          <t>0,36; 0,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,31</t>
+          <t>0,18; 0,31</t>
         </is>
       </c>
     </row>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,43</t>
+          <t>0,3; 0,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,56</t>
+          <t>0,32; 0,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,44</t>
+          <t>0,28; 0,44</t>
         </is>
       </c>
     </row>
@@ -1421,17 +1421,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,24</t>
+          <t>0,13; 0,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,36</t>
+          <t>0,15; 0,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,21</t>
+          <t>0,05; 0,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,42; 0,57</t>
+          <t>0,41; 0,56</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,43</t>
+          <t>0,32; 0,42</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,26</t>
+          <t>0,2; 0,26</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,26</t>
+          <t>0,18; 0,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,39; 0,45</t>
+          <t>0,39; 0,44</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,39; 0,45</t>
+          <t>0,38; 0,45</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">

--- a/data/trans_orig/Q17B-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q17B-Clase-trans_orig.xlsx
@@ -683,27 +683,27 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
+          <t>0,36</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0,27</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>0,31</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
           <t>0,34</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0,24</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0,27</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>0,31</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,33</t>
         </is>
       </c>
     </row>
@@ -726,22 +726,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,35</t>
+          <t>0,23; 0,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,41</t>
+          <t>0,26; 0,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,33</t>
+          <t>0,21; 0,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,43</t>
+          <t>0,25; 0,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,4</t>
+          <t>0,31; 0,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,37</t>
+          <t>0,27; 0,38</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,38</t>
+          <t>0,3; 0,41</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,31</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,28</t>
+          <t>0,27</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,4</t>
+          <t>0,17; 0,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -871,22 +871,22 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,32</t>
+          <t>0,2; 0,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,36</t>
+          <t>0,25; 0,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,45</t>
+          <t>0,29; 0,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,34</t>
+          <t>0,23; 0,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,34</t>
+          <t>0,22; 0,35</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,33</t>
+          <t>0,23; 0,32</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,32</t>
+          <t>0,24; 0,31</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,17</t>
+          <t>0,27</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,21</t>
+          <t>0,29</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,39</t>
+          <t>0,27; 0,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1011,22 +1011,22 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,29</t>
+          <t>0,21; 0,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,66</t>
+          <t>0,34; 0,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,35; 0,52</t>
+          <t>0,34; 0,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,5</t>
+          <t>0,32; 0,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,36</t>
+          <t>0,25; 0,36</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,31</t>
+          <t>0,25; 0,35</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>0,25</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,27</t>
+          <t>0,35</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,27</t>
+          <t>0,29</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,32</t>
+          <t>0,25; 0,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1151,12 +1151,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,3</t>
+          <t>0,22; 0,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 0,46</t>
+          <t>0,35; 0,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1166,12 +1166,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,49</t>
+          <t>0,36; 0,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,37</t>
+          <t>0,31; 0,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,42</t>
+          <t>0,33; 0,41</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,31</t>
+          <t>0,27; 0,32</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,22</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>0,34</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,33</t>
+          <t>0,28</t>
         </is>
       </c>
     </row>
@@ -1286,17 +1286,17 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,45</t>
+          <t>0,3; 0,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,29</t>
+          <t>0,16; 0,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 0,48</t>
+          <t>0,36; 0,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,55</t>
+          <t>0,3; 0,37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,41</t>
+          <t>0,32; 0,41</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1331,14 +1331,14 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,44</t>
+          <t>0,26; 0,32</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1421,17 +1421,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,25</t>
+          <t>0,12; 0,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,37</t>
+          <t>0,15; 0,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,19</t>
+          <t>0,05; 0,18</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1441,17 +1441,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,49</t>
+          <t>0,36; 0,48</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,41; 0,56</t>
+          <t>0,42; 0,57</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,31</t>
+          <t>0,24; 0,31</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,42</t>
+          <t>0,32; 0,43</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,37; 0,49</t>
+          <t>0,37; 0,48</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,26</t>
+          <t>0,2; 0,27</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,24</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,14 +1523,14 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
+          <t>0,32</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>0,31</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0,31</t>
-        </is>
-      </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0,35</t>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,27</t>
+          <t>0,29</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,26</t>
+          <t>0,22; 0,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1581,17 +1581,17 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,39; 0,44</t>
+          <t>0,39; 0,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,38; 0,45</t>
+          <t>0,39; 0,45</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,36</t>
+          <t>0,3; 0,34</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,37</t>
+          <t>0,34; 0,38</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,3</t>
+          <t>0,27; 0,3</t>
         </is>
       </c>
     </row>
